--- a/AAII_Financials/Quarterly/DBSDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBSDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="92">
   <si>
     <t>DBSDY</t>
   </si>
@@ -656,72 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -761,8 +764,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -802,8 +808,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,8 +852,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -860,8 +872,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -901,8 +914,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -942,8 +958,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -983,8 +1002,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1024,8 +1046,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1038,8 +1063,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1079,8 +1105,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1120,8 +1149,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1137,8 +1169,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1178,8 +1211,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1219,8 +1255,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1260,8 +1299,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1301,8 +1343,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1342,8 +1387,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1383,8 +1431,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1424,8 +1475,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1465,8 +1519,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1506,8 +1563,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1547,8 +1607,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1588,8 +1651,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1629,8 +1695,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1670,8 +1739,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1711,8 +1783,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1752,8 +1827,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1793,54 +1871,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1856,8 +1940,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1873,199 +1958,212 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25229300</v>
+      </c>
+      <c r="E41" s="3">
         <v>36060400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35811000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34696500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38092800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30209700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25773300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32796900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35856400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>25773300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>32796900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27073900</v>
+      </c>
+      <c r="E42" s="3">
         <v>18364500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18935900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20441100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17694600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17197800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38413100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33512100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28377900</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>38413100</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>33512100</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>82234600</v>
+      </c>
+      <c r="E43" s="3">
         <v>85642500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>66021100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>71772100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58243200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56839700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49346100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50810700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37400400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>49346100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>50810700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>75700</v>
+      </c>
+      <c r="E44" s="3">
         <v>90200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>92700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>76200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>80400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>95500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>106400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>118600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>149500</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>106400</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>118600</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
         <v>6435900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
         <v>5129900</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>3263000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>2279900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2075,175 +2173,190 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>2279900</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>145043200</v>
+      </c>
+      <c r="E46" s="3">
         <v>157778900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>129941500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>143521500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>120879200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119383500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119856100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>131745300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>107566900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>119856100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>131745300</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>206246900</v>
+      </c>
+      <c r="E47" s="3">
         <v>163791100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>161979800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>138974200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>126059100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>117268200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>112860000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>106448100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>99355900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>112860000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>106448100</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2942600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1490400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2875900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1639100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2651900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1774300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2375600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1505000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2280800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>2375600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>1505000</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4860600</v>
+      </c>
+      <c r="E49" s="3">
         <v>5915000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5023800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5664800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4718200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5775300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3948700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4863300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3849900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>3948700</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>4863300</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2283,8 +2396,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2324,49 +2440,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24355300</v>
+      </c>
+      <c r="E52" s="3">
         <v>22416700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21261200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>203000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15145200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13811000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17758900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>13811000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2406,49 +2528,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>746159100</v>
+      </c>
+      <c r="E54" s="3">
         <v>697766300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>661166200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>606132300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>582845400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>560102000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>560027000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>554396400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>535970600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>560027000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>554396400</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2464,8 +2592,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2481,117 +2610,124 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>493167400</v>
+      </c>
+      <c r="E57" s="3">
         <v>474272100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>450752000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>411599200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>406524000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>405399500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>384287000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>393031300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>379407600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>384287000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>393031300</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>69509800</v>
+      </c>
+      <c r="E58" s="3">
         <v>120135600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>58458400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>98884800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42127900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>71949500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>58107300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>85051400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51737700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>58107300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>85051400</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>7088200</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
         <v>6778500</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>5036600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>5643400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2601,134 +2737,146 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>5643400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>562677200</v>
+      </c>
+      <c r="E60" s="3">
         <v>602982400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>509210400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>518791000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>448651900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>483967500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>442394400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>484630800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>431145300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>442394400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>484630800</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>95148700</v>
+      </c>
+      <c r="E61" s="3">
         <v>22269000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>77231700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19351500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>65539500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19741800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>55586200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17821400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42526900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>55586200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>17821400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>34073400</v>
+      </c>
+      <c r="E62" s="3">
         <v>18373900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20842700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16947400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20340700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8570100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18498700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8694400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21997700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>18498700</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>8694400</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2768,8 +2916,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2809,8 +2960,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2850,49 +3004,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>691899300</v>
+      </c>
+      <c r="E66" s="3">
         <v>644186500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>607284700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>555695900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>534532100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>512943000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>516479200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>511832700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>495669900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>516479200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>511832700</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2908,8 +3068,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2949,8 +3110,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2990,8 +3154,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3031,8 +3198,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3072,49 +3242,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>43986100</v>
+      </c>
+      <c r="E72" s="3">
         <v>43058400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>42896300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>38954400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>37440000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>36435000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33978900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33073500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29973600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>33978900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>33073500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3154,8 +3330,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3195,8 +3374,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3236,49 +3418,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>54220300</v>
+      </c>
+      <c r="E76" s="3">
         <v>53541700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53845400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50401900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48170900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47021100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43409600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42425800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>40163500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43023100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43409600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42780200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>42425800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3318,54 +3506,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3405,8 +3599,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3422,8 +3619,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3463,8 +3661,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3504,8 +3705,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3545,8 +3749,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3586,8 +3793,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3627,8 +3837,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3668,8 +3881,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3709,8 +3925,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3726,8 +3945,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3767,8 +3987,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3808,8 +4031,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3849,8 +4075,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3890,8 +4119,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3907,8 +4139,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3948,8 +4181,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3989,8 +4225,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4030,8 +4269,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4071,8 +4313,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4112,8 +4357,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4153,8 +4401,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4182,8 +4433,8 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
@@ -4192,6 +4443,9 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
